--- a/phase1/topsis.xlsx
+++ b/phase1/topsis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m41den/Downloads/pm/PmProject/phase1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7AEC9D-8BC3-B44B-9246-1B40DA3B63E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF803E4-9B3B-4E08-AFFB-404F1F00E826}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Концепции и критерии" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -417,12 +417,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -445,9 +439,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -465,7 +465,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -479,7 +479,12 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>CCᵢ по альтернативам</a:t>
+              <a:rPr lang="de-DE"/>
+              <a:t>CCᵢ </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>по альтернативам</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -616,6 +621,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="de-DE"/>
                   <a:t>CCᵢ</a:t>
                 </a:r>
               </a:p>
@@ -966,7 +972,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -974,14 +980,14 @@
     <col min="4" max="29" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -992,7 +998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1047,7 +1053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1091,7 +1097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1124,7 +1130,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1</v>
       </c>
@@ -1135,7 +1141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -1157,18 +1163,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
       <c r="C24" s="7" t="s">
         <v>47</v>
@@ -1185,23 +1191,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="29" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>53</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>54</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>55</v>
       </c>
@@ -1257,7 +1263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>56</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
@@ -1285,15 +1291,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1307,33 +1313,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="29" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-    </row>
-    <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1353,7 +1359,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -1393,7 +1399,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1419,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>9</v>
       </c>
@@ -1433,7 +1439,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
@@ -1453,7 +1459,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>61</v>
       </c>
@@ -1473,17 +1479,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-    </row>
-    <row r="13" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+    </row>
+    <row r="13" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>1</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>6</v>
       </c>
@@ -1523,7 +1529,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>7</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1569,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>9</v>
       </c>
@@ -1583,7 +1589,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>10</v>
       </c>
@@ -1603,7 +1609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
@@ -1623,17 +1629,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-    </row>
-    <row r="22" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+    </row>
+    <row r="22" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>1</v>
       </c>
@@ -1653,7 +1659,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>6</v>
       </c>
@@ -1673,7 +1679,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>7</v>
       </c>
@@ -1693,7 +1699,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>8</v>
       </c>
@@ -1713,7 +1719,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>9</v>
       </c>
@@ -1733,7 +1739,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>10</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>61</v>
       </c>
@@ -1799,83 +1805,83 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="29" width="7.5" customWidth="1"/>
+    <col min="2" max="29" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-    </row>
-    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26" t="s">
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26" t="s">
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26" t="s">
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26" t="s">
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-    </row>
-    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>50</v>
@@ -1923,7 +1929,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
@@ -1988,7 +1994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
@@ -2183,7 +2189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>61</v>
       </c>
@@ -2313,57 +2319,57 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-    </row>
-    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26" t="s">
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26" t="s">
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-    </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="9" t="s">
         <v>50</v>
@@ -2411,7 +2417,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>6</v>
       </c>
@@ -2476,7 +2482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>7</v>
       </c>
@@ -2541,7 +2547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>8</v>
       </c>
@@ -2606,7 +2612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>9</v>
       </c>
@@ -2671,7 +2677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>10</v>
       </c>
@@ -2736,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>61</v>
       </c>
@@ -2801,57 +2807,57 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" s="24" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-    </row>
-    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26" t="s">
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26" t="s">
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26" t="s">
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26" t="s">
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-    </row>
-    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
         <v>50</v>
@@ -2899,7 +2905,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>6</v>
       </c>
@@ -2964,7 +2970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>7</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>8</v>
       </c>
@@ -3094,7 +3100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>9</v>
       </c>
@@ -3159,7 +3165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>10</v>
       </c>
@@ -3224,7 +3230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>61</v>
       </c>
@@ -3291,6 +3297,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="K14:M14"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="N24:P24"/>
@@ -3307,9 +3316,6 @@
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A23:P23"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="A13:P13"/>
-    <mergeCell ref="K14:M14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3318,65 +3324,65 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="16" width="7.5" customWidth="1"/>
+    <col min="2" max="16" width="7.42578125" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
-    <col min="18" max="29" width="7.5" customWidth="1"/>
+    <col min="18" max="29" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-    </row>
-    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="2" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26" t="s">
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26" t="s">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26" t="s">
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-    </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="9" t="s">
         <v>50</v>
@@ -3424,7 +3430,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
@@ -3489,7 +3495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
@@ -3619,7 +3625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
@@ -3684,7 +3690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
@@ -3749,7 +3755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>66</v>
       </c>
@@ -3814,57 +3820,57 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-    </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+    </row>
+    <row r="12" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26" t="s">
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26" t="s">
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26" t="s">
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26" t="s">
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-    </row>
-    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
         <v>50</v>
@@ -3912,7 +3918,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>6</v>
       </c>
@@ -3977,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>7</v>
       </c>
@@ -4042,7 +4048,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>8</v>
       </c>
@@ -4107,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>9</v>
       </c>
@@ -4172,7 +4178,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>10</v>
       </c>
@@ -4237,57 +4243,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+    <row r="20" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-    </row>
-    <row r="21" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+    </row>
+    <row r="21" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26" t="s">
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26" t="s">
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26" t="s">
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26" t="s">
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-    </row>
-    <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
         <v>50</v>
@@ -4335,7 +4341,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>6</v>
       </c>
@@ -4400,7 +4406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>7</v>
       </c>
@@ -4465,7 +4471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>8</v>
       </c>
@@ -4530,7 +4536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>9</v>
       </c>
@@ -4595,7 +4601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>10</v>
       </c>
@@ -4660,7 +4666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>69</v>
       </c>
@@ -4725,7 +4731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>70</v>
       </c>
@@ -4790,497 +4796,497 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
+    <row r="31" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-    </row>
-    <row r="32" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26" t="s">
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26" t="s">
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26" t="s">
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26" t="s">
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
       <c r="Q32" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="25">
         <f>SQRT((1/3)*((B23-B$28)^2+(C23-C$28)^2+(D23-D$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="27">
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="25">
         <f>SQRT((1/3)*((E23-E$28)^2+(F23-F$28)^2+(G23-G$28)^2))</f>
         <v>0.618927852198213</v>
       </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="27">
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="25">
         <f>SQRT((1/3)*((H23-H$28)^2+(I23-I$28)^2+(J23-J$28)^2))</f>
         <v>0.75231019836084934</v>
       </c>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="27">
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="25">
         <f>SQRT((1/3)*((K23-K$28)^2+(L23-L$28)^2+(M23-M$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="27">
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="25">
         <f>SQRT((1/3)*((N23-N$28)^2+(O23-O$28)^2+(P23-P$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
       <c r="Q33" s="15">
         <f>SUM(B33,E33,H33,K33,N33)</f>
         <v>1.3712380505590622</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="25">
         <f>SQRT((1/3)*((B24-B$28)^2+(C24-C$28)^2+(D24-D$28)^2))</f>
         <v>3.7228585606250673</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="27">
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="25">
         <f>SQRT((1/3)*((E24-E$28)^2+(F24-F$28)^2+(G24-G$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="27">
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="25">
         <f>SQRT((1/3)*((H24-H$28)^2+(I24-I$28)^2+(J24-J$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="27">
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="25">
         <f>SQRT((1/3)*((K24-K$28)^2+(L24-L$28)^2+(M24-M$28)^2))</f>
         <v>3.4995880902329941</v>
       </c>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="27">
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="25">
         <f>SQRT((1/3)*((N24-N$28)^2+(O24-O$28)^2+(P24-P$28)^2))</f>
         <v>2.6171674793558237</v>
       </c>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
       <c r="Q34" s="15">
         <f>SUM(B34,E34,H34,K34,N34)</f>
         <v>9.8396141302138851</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="25">
         <f>SQRT((1/3)*((B25-B$28)^2+(C25-C$28)^2+(D25-D$28)^2))</f>
         <v>1.1743330321574437</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="27">
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="25">
         <f>SQRT((1/3)*((E25-E$28)^2+(F25-F$28)^2+(G25-G$28)^2))</f>
         <v>0.82263364192383603</v>
       </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="27">
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="25">
         <f>SQRT((1/3)*((H25-H$28)^2+(I25-I$28)^2+(J25-J$28)^2))</f>
         <v>1.5985310535733828</v>
       </c>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="27">
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="25">
         <f>SQRT((1/3)*((K25-K$28)^2+(L25-L$28)^2+(M25-M$28)^2))</f>
         <v>1.1743330321574437</v>
       </c>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="27">
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="25">
         <f>SQRT((1/3)*((N25-N$28)^2+(O25-O$28)^2+(P25-P$28)^2))</f>
         <v>1.1743330321574441</v>
       </c>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
       <c r="Q35" s="15">
         <f>SUM(B35,E35,H35,K35,N35)</f>
         <v>5.9441637919695509</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="25">
         <f>SQRT((1/3)*((B26-B$28)^2+(C26-C$28)^2+(D26-D$28)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="27">
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="25">
         <f>SQRT((1/3)*((E26-E$28)^2+(F26-F$28)^2+(G26-G$28)^2))</f>
         <v>0.82263364192383603</v>
       </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="27">
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="25">
         <f>SQRT((1/3)*((H26-H$28)^2+(I26-I$28)^2+(J26-J$28)^2))</f>
         <v>0.18532230862876881</v>
       </c>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="27">
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="25">
         <f>SQRT((1/3)*((K26-K$28)^2+(L26-L$28)^2+(M26-M$28)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="27">
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="25">
         <f>SQRT((1/3)*((N26-N$28)^2+(O26-O$28)^2+(P26-P$28)^2))</f>
         <v>3.960712410457734</v>
       </c>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
       <c r="Q36" s="15">
         <f>SUM(B36,E36,H36,K36,N36)</f>
         <v>12.890093181925806</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="25">
         <f>SQRT((1/3)*((B27-B$28)^2+(C27-C$28)^2+(D27-D$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="27">
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="25">
         <f>SQRT((1/3)*((E27-E$28)^2+(F27-F$28)^2+(G27-G$28)^2))</f>
         <v>2.0100342705120307</v>
       </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="27">
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25">
         <f>SQRT((1/3)*((H27-H$28)^2+(I27-I$28)^2+(J27-J$28)^2))</f>
         <v>1.4521793533365543</v>
       </c>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="27">
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="25">
         <f>SQRT((1/3)*((K27-K$28)^2+(L27-L$28)^2+(M27-M$28)^2))</f>
         <v>0</v>
       </c>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="27">
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="25">
         <f>SQRT((1/3)*((N27-N$28)^2+(O27-O$28)^2+(P27-P$28)^2))</f>
         <v>1.4599950795367445</v>
       </c>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
       <c r="Q37" s="15">
         <f>SUM(B37,E37,H37,K37,N37)</f>
         <v>4.9222087033853299</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
+    <row r="39" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-    </row>
-    <row r="40" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+    </row>
+    <row r="40" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26" t="s">
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26" t="s">
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26" t="s">
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26" t="s">
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
       <c r="Q40" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="25">
         <f>SQRT((1/3)*((B23-B$29)^2+(C23-C$29)^2+(D23-D$29)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="27">
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="25">
         <f>SQRT((1/3)*((E23-E$29)^2+(F23-F$29)^2+(G23-G$29)^2))</f>
         <v>1.5560127357434006</v>
       </c>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="27">
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="25">
         <f>SQRT((1/3)*((H23-H$29)^2+(I23-I$29)^2+(J23-J$29)^2))</f>
         <v>1.0640227864896414</v>
       </c>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="27">
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="25">
         <f>SQRT((1/3)*((K23-K$29)^2+(L23-L$29)^2+(M23-M$29)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="27">
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="25">
         <f>SQRT((1/3)*((N23-N$29)^2+(O23-O$29)^2+(P23-P$29)^2))</f>
         <v>3.960712410457734</v>
       </c>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
       <c r="Q41" s="15">
         <f>SUM(B41,E41,H41,K41,N41)</f>
         <v>14.502172753606242</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="25">
         <f>SQRT((1/3)*((B24-B$29)^2+(C24-C$29)^2+(D24-D$29)^2))</f>
         <v>0.32787793065089871</v>
       </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="27">
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="25">
         <f>SQRT((1/3)*((E24-E$29)^2+(F24-F$29)^2+(G24-G$29)^2))</f>
         <v>2.0100342705120307</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="27">
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="25">
         <f>SQRT((1/3)*((H24-H$29)^2+(I24-I$29)^2+(J24-J$29)^2))</f>
         <v>1.5985310535733828</v>
       </c>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="27">
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="25">
         <f>SQRT((1/3)*((K24-K$29)^2+(L24-L$29)^2+(M24-M$29)^2))</f>
         <v>0.65575586130179697</v>
       </c>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="27">
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="25">
         <f>SQRT((1/3)*((N24-N$29)^2+(O24-O$29)^2+(P24-P$29)^2))</f>
         <v>1.5168614867563128</v>
       </c>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
       <c r="Q42" s="15">
         <f>SUM(B42,E42,H42,K42,N42)</f>
         <v>6.1090606027944219</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="25">
         <f>SQRT((1/3)*((B25-B$29)^2+(C25-C$29)^2+(D25-D$29)^2))</f>
         <v>3.1008059780907198</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="27">
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="25">
         <f>SQRT((1/3)*((E25-E$29)^2+(F25-F$29)^2+(G25-G$29)^2))</f>
         <v>1.417765651353639</v>
       </c>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="27">
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="25">
         <f>SQRT((1/3)*((H25-H$29)^2+(I25-I$29)^2+(J25-J$29)^2))</f>
         <v>0</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="27">
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="25">
         <f>SQRT((1/3)*((K25-K$29)^2+(L25-L$29)^2+(M25-M$29)^2))</f>
         <v>3.1008059780907198</v>
       </c>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="27">
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="25">
         <f>SQRT((1/3)*((N25-N$29)^2+(O25-O$29)^2+(P25-P$29)^2))</f>
         <v>3.1008059780907198</v>
       </c>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
       <c r="Q43" s="15">
         <f>SUM(B43,E43,H43,K43,N43)</f>
         <v>10.720183585625797</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="25">
         <f>SQRT((1/3)*((B26-B$29)^2+(C26-C$29)^2+(D26-D$29)^2))</f>
         <v>0</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="27">
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="25">
         <f>SQRT((1/3)*((E26-E$29)^2+(F26-F$29)^2+(G26-G$29)^2))</f>
         <v>1.417765651353639</v>
       </c>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="27">
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="25">
         <f>SQRT((1/3)*((H26-H$29)^2+(I26-I$29)^2+(J26-J$29)^2))</f>
         <v>1.4521793533365543</v>
       </c>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="27">
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="25">
         <f>SQRT((1/3)*((K26-K$29)^2+(L26-L$29)^2+(M26-M$29)^2))</f>
         <v>0</v>
       </c>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="27">
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="25">
         <f>SQRT((1/3)*((N26-N$29)^2+(O26-O$29)^2+(P26-P$29)^2))</f>
         <v>0</v>
       </c>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
       <c r="Q44" s="15">
         <f>SUM(B44,E44,H44,K44,N44)</f>
         <v>2.8699450046901935</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="25">
         <f>SQRT((1/3)*((B27-B$29)^2+(C27-C$29)^2+(D27-D$29)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="27">
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="25">
         <f>SQRT((1/3)*((E27-E$29)^2+(F27-F$29)^2+(G27-G$29)^2))</f>
         <v>0</v>
       </c>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="27">
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="25">
         <f>SQRT((1/3)*((H27-H$29)^2+(I27-I$29)^2+(J27-J$29)^2))</f>
         <v>0.18532230862876881</v>
       </c>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="27">
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="25">
         <f>SQRT((1/3)*((K27-K$29)^2+(L27-L$29)^2+(M27-M$29)^2))</f>
         <v>3.9607124104577336</v>
       </c>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="27">
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="25">
         <f>SQRT((1/3)*((N27-N$29)^2+(O27-O$29)^2+(P27-P$29)^2))</f>
         <v>2.9038688679546252</v>
       </c>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="26"/>
       <c r="Q45" s="15">
         <f>SUM(B45,E45,H45,K45,N45)</f>
         <v>11.01061599749886</v>
@@ -5288,6 +5294,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H32:J32"/>
     <mergeCell ref="A20:P20"/>
     <mergeCell ref="K43:M43"/>
     <mergeCell ref="K2:M2"/>
@@ -5304,70 +5374,6 @@
     <mergeCell ref="H41:J41"/>
     <mergeCell ref="N43:P43"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="H36:J36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5376,23 +5382,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="29" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -5409,7 +5415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
@@ -5451,7 +5457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
@@ -5472,7 +5478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
@@ -5493,7 +5499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
@@ -5514,27 +5520,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="27" t="str">
         <f>INDEX($A$4:$A$8,MATCH(MAX($D$4:$D$8),$D$4:$D$8,0))</f>
         <v>Сплит</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
